--- a/convert-to-excel/inventories_demo.xlsx
+++ b/convert-to-excel/inventories_demo.xlsx
@@ -427,91 +427,91 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HVAC Filter - High Capacity</v>
+        <v>Hydraulic Oil - 20L</v>
       </c>
       <c r="B2" t="str">
-        <v>INV-FILT-001</v>
+        <v>INV-OIL-500</v>
       </c>
       <c r="C2" t="str">
-        <v>Filters</v>
+        <v>Lubricants</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="G2" t="str">
-        <v>pcs</v>
+        <v>canisters</v>
       </c>
       <c r="H2" t="str">
-        <v>Warehouse A - Shelf 1</v>
+        <v>Oil Shed - Section B</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Industrial Lubricant - 5L</v>
+        <v>N95 Dust Masks</v>
       </c>
       <c r="B3" t="str">
-        <v>INV-LUB-005</v>
+        <v>INV-PPE-010</v>
       </c>
       <c r="C3" t="str">
-        <v>Lubricants</v>
+        <v>Safety Equipment</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>450</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="str">
-        <v>bottles</v>
+        <v>pcs</v>
       </c>
       <c r="H3" t="str">
-        <v>Main Store Room</v>
+        <v>Safety Locker 3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Safety Googles - Clear</v>
+        <v>Bearing 6205-2RS</v>
       </c>
       <c r="B4" t="str">
-        <v>INV-SAF-102</v>
+        <v>INV-MECH-992</v>
       </c>
       <c r="C4" t="str">
-        <v>Safety Equipment</v>
+        <v>Mechanical Parts</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
         <v>15</v>
       </c>
-      <c r="F4">
-        <v>25</v>
-      </c>
       <c r="G4" t="str">
-        <v>pairs</v>
+        <v>pcs</v>
       </c>
       <c r="H4" t="str">
-        <v>Safety Cabinet 1</v>
+        <v>Small Parts Bin - Row 2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Copper Pipe - 1/2 inch</v>
+        <v>Network Patch Cable - 3m</v>
       </c>
       <c r="B5" t="str">
-        <v>INV-PLM-003</v>
+        <v>INV-IT-442</v>
       </c>
       <c r="C5" t="str">
-        <v>Plumbing</v>
+        <v>IT Supplies</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -520,39 +520,39 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="str">
-        <v>meters</v>
+        <v>pcs</v>
       </c>
       <c r="H5" t="str">
-        <v>Plumbing Section - Floor 2</v>
+        <v>Server Room Cabinet</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LED Bulb - 12W</v>
+        <v>Industrial Degreaser - 10L</v>
       </c>
       <c r="B6" t="str">
-        <v>INV-ELE-201</v>
+        <v>INV-CHEM-302</v>
       </c>
       <c r="C6" t="str">
-        <v>Electrical</v>
+        <v>Chemicals</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>650</v>
       </c>
       <c r="G6" t="str">
-        <v>units</v>
+        <v>drums</v>
       </c>
       <c r="H6" t="str">
-        <v>Electrical Bin 4</v>
+        <v>Hazardous Materials Area</v>
       </c>
     </row>
   </sheetData>
